--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1069DC7A-E455-4287-B612-71418CC296EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FB0113-29E2-478A-AC96-D306A07D1689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>HAPPY FAMILY TIME</t>
+  </si>
+  <si>
+    <t>FAMILY IS ALL</t>
   </si>
 </sst>
 </file>
@@ -2284,26 +2287,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="14" t="str">
+      <c r="A32" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="15">
+        <v>360</v>
+      </c>
+      <c r="C32" s="15">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15">
+        <v>240</v>
+      </c>
+      <c r="E32" s="15">
+        <v>0</v>
+      </c>
+      <c r="F32" s="15">
+        <v>0</v>
+      </c>
+      <c r="G32" s="15">
+        <v>0</v>
+      </c>
+      <c r="H32" s="15">
+        <v>50</v>
+      </c>
+      <c r="I32" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="14" t="str">
+        <v>650</v>
+      </c>
+      <c r="J32" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="33" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38FB0113-29E2-478A-AC96-D306A07D1689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C347486-469C-4662-9290-C6643ABDBB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2333,26 +2333,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="14" t="str">
+      <c r="A33" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B33" s="15">
+        <v>270</v>
+      </c>
+      <c r="C33" s="15">
+        <v>120</v>
+      </c>
+      <c r="D33" s="15">
+        <v>240</v>
+      </c>
+      <c r="E33" s="15">
+        <v>150</v>
+      </c>
+      <c r="F33" s="15">
+        <v>300</v>
+      </c>
+      <c r="G33" s="15">
+        <v>6</v>
+      </c>
+      <c r="H33" s="15">
+        <v>50</v>
+      </c>
+      <c r="I33" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="14" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J33" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="34" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C347486-469C-4662-9290-C6643ABDBB39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93573524-DAE6-40C1-A4AE-759CA7B80E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2379,26 +2379,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="14" t="str">
+      <c r="A34" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B34" s="15">
+        <v>450</v>
+      </c>
+      <c r="C34" s="15">
+        <v>60</v>
+      </c>
+      <c r="D34" s="15">
+        <v>120</v>
+      </c>
+      <c r="E34" s="15">
+        <v>50</v>
+      </c>
+      <c r="F34" s="15">
+        <v>300</v>
+      </c>
+      <c r="G34" s="15">
+        <v>6</v>
+      </c>
+      <c r="H34" s="15">
+        <v>0</v>
+      </c>
+      <c r="I34" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="14" t="str">
+        <v>980</v>
+      </c>
+      <c r="J34" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93573524-DAE6-40C1-A4AE-759CA7B80E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7627C7E-42C3-4429-A404-4494E0547D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>FAMILY IS ALL</t>
+  </si>
+  <si>
+    <t>MUNDANE DAY</t>
   </si>
 </sst>
 </file>
@@ -2425,26 +2428,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="14" t="str">
+      <c r="A35" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B35" s="15">
+        <v>240</v>
+      </c>
+      <c r="C35" s="15">
+        <v>140</v>
+      </c>
+      <c r="D35" s="15">
+        <v>150</v>
+      </c>
+      <c r="E35" s="15">
+        <v>100</v>
+      </c>
+      <c r="F35" s="15">
+        <v>250</v>
+      </c>
+      <c r="G35" s="15">
+        <v>5</v>
+      </c>
+      <c r="H35" s="15">
+        <v>30</v>
+      </c>
+      <c r="I35" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="14" t="str">
+        <v>910</v>
+      </c>
+      <c r="J35" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="36" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7627C7E-42C3-4429-A404-4494E0547D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805EA716-E44B-4E2A-B2E9-95E3260CF47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>MUNDANE DAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STARTED WELL </t>
   </si>
 </sst>
 </file>
@@ -2474,26 +2477,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="14" t="str">
+      <c r="A36" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B36" s="15">
+        <v>330</v>
+      </c>
+      <c r="C36" s="15">
+        <v>100</v>
+      </c>
+      <c r="D36" s="15">
+        <v>120</v>
+      </c>
+      <c r="E36" s="15">
+        <v>0</v>
+      </c>
+      <c r="F36" s="15">
+        <v>150</v>
+      </c>
+      <c r="G36" s="15">
+        <v>3</v>
+      </c>
+      <c r="H36" s="15">
+        <v>20</v>
+      </c>
+      <c r="I36" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="14" t="str">
+        <v>720</v>
+      </c>
+      <c r="J36" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="37" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805EA716-E44B-4E2A-B2E9-95E3260CF47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6018535-E24E-4504-9739-518988B4FB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t xml:space="preserve">STARTED WELL </t>
+  </si>
+  <si>
+    <t>PREPARING</t>
   </si>
 </sst>
 </file>
@@ -2523,26 +2526,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="14" t="str">
+      <c r="A37" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B37" s="15">
+        <v>460</v>
+      </c>
+      <c r="C37" s="15">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15">
+        <v>300</v>
+      </c>
+      <c r="E37" s="15">
+        <v>0</v>
+      </c>
+      <c r="F37" s="15">
+        <v>0</v>
+      </c>
+      <c r="G37" s="15">
+        <v>0</v>
+      </c>
+      <c r="H37" s="15">
+        <v>50</v>
+      </c>
+      <c r="I37" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="14" t="str">
+        <v>810</v>
+      </c>
+      <c r="J37" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="38" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6018535-E24E-4504-9739-518988B4FB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E10AFAB-6693-4BDC-B4E1-52816304B9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>PREPARING</t>
+  </si>
+  <si>
+    <t>PICKING UP</t>
   </si>
 </sst>
 </file>
@@ -2572,26 +2575,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="14" t="str">
+      <c r="A38" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B38" s="15">
+        <v>270</v>
+      </c>
+      <c r="C38" s="15">
+        <v>130</v>
+      </c>
+      <c r="D38" s="15">
+        <v>270</v>
+      </c>
+      <c r="E38" s="15">
+        <v>150</v>
+      </c>
+      <c r="F38" s="15">
+        <v>250</v>
+      </c>
+      <c r="G38" s="15">
+        <v>5</v>
+      </c>
+      <c r="H38" s="15">
+        <v>120</v>
+      </c>
+      <c r="I38" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="14" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J38" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="39" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E10AFAB-6693-4BDC-B4E1-52816304B9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BD10CF-AC8A-45FE-9DEE-8F75C3311F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>PICKING UP</t>
+  </si>
+  <si>
+    <t>MAINTAINING IT</t>
   </si>
 </sst>
 </file>
@@ -2621,26 +2624,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="14" t="str">
+      <c r="A39" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B39" s="15">
+        <v>280</v>
+      </c>
+      <c r="C39" s="15">
+        <v>70</v>
+      </c>
+      <c r="D39" s="15">
+        <v>210</v>
+      </c>
+      <c r="E39" s="15">
+        <v>120</v>
+      </c>
+      <c r="F39" s="15">
+        <v>300</v>
+      </c>
+      <c r="G39" s="15">
+        <v>6</v>
+      </c>
+      <c r="H39" s="15">
+        <v>120</v>
+      </c>
+      <c r="I39" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="14" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J39" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="40" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7BD10CF-AC8A-45FE-9DEE-8F75C3311F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82309204-E036-41A1-BD24-9A29F6C29F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t>MAINTAINING IT</t>
+  </si>
+  <si>
+    <t>BIT CONSISTENCE</t>
   </si>
 </sst>
 </file>
@@ -2670,26 +2673,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="14" t="str">
+      <c r="A40" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B40" s="15">
+        <v>300</v>
+      </c>
+      <c r="C40" s="15">
+        <v>80</v>
+      </c>
+      <c r="D40" s="15">
+        <v>190</v>
+      </c>
+      <c r="E40" s="15">
+        <v>120</v>
+      </c>
+      <c r="F40" s="15">
+        <v>300</v>
+      </c>
+      <c r="G40" s="15">
+        <v>6</v>
+      </c>
+      <c r="H40" s="15">
+        <v>120</v>
+      </c>
+      <c r="I40" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="14" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J40" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="41" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82309204-E036-41A1-BD24-9A29F6C29F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0522A7FF-C3B7-4A0F-8AC5-551DD8CB1CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>BIT CONSISTENCE</t>
+  </si>
+  <si>
+    <t>SLOW AGAIN</t>
   </si>
 </sst>
 </file>
@@ -2719,26 +2722,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="14" t="str">
+      <c r="A41" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B41" s="15">
+        <v>420</v>
+      </c>
+      <c r="C41" s="15">
+        <v>0</v>
+      </c>
+      <c r="D41" s="15">
+        <v>240</v>
+      </c>
+      <c r="E41" s="15">
+        <v>0</v>
+      </c>
+      <c r="F41" s="15">
+        <v>150</v>
+      </c>
+      <c r="G41" s="15">
+        <v>3</v>
+      </c>
+      <c r="H41" s="15">
+        <v>80</v>
+      </c>
+      <c r="I41" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="14" t="str">
+        <v>890</v>
+      </c>
+      <c r="J41" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="42" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0522A7FF-C3B7-4A0F-8AC5-551DD8CB1CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BCAFAF-0FE3-4F2A-920A-9AC3F654C379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>SLOW AGAIN</t>
+  </si>
+  <si>
+    <t>GOOD GOING</t>
   </si>
 </sst>
 </file>
@@ -2768,26 +2771,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="14" t="str">
+      <c r="A42" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B42" s="15">
+        <v>450</v>
+      </c>
+      <c r="C42" s="15">
+        <v>0</v>
+      </c>
+      <c r="D42" s="15">
+        <v>300</v>
+      </c>
+      <c r="E42" s="15">
+        <v>0</v>
+      </c>
+      <c r="F42" s="15">
+        <v>0</v>
+      </c>
+      <c r="G42" s="15">
+        <v>0</v>
+      </c>
+      <c r="H42" s="15">
+        <v>120</v>
+      </c>
+      <c r="I42" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="14" t="str">
+        <v>870</v>
+      </c>
+      <c r="J42" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="43" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BCAFAF-0FE3-4F2A-920A-9AC3F654C379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD679D5-65BD-4C5C-84B7-AA86D96A3214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>GOOD GOING</t>
+  </si>
+  <si>
+    <t>REST TIME</t>
   </si>
 </sst>
 </file>
@@ -2817,26 +2820,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="14" t="str">
+      <c r="A43" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B43" s="15">
+        <v>600</v>
+      </c>
+      <c r="C43" s="15">
+        <v>0</v>
+      </c>
+      <c r="D43" s="15">
+        <v>50</v>
+      </c>
+      <c r="E43" s="15">
+        <v>0</v>
+      </c>
+      <c r="F43" s="15">
+        <v>0</v>
+      </c>
+      <c r="G43" s="15">
+        <v>0</v>
+      </c>
+      <c r="H43" s="15">
+        <v>0</v>
+      </c>
+      <c r="I43" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="14" t="str">
+        <v>650</v>
+      </c>
+      <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="44" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CD679D5-65BD-4C5C-84B7-AA86D96A3214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E25DDF4-1FA9-4621-831F-814DF4C24081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>REST TIME</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>NO PROGRESS</t>
   </si>
 </sst>
 </file>
@@ -2866,26 +2872,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="14" t="str">
+      <c r="A44" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B44" s="15">
+        <v>580</v>
+      </c>
+      <c r="C44" s="15">
+        <v>0</v>
+      </c>
+      <c r="D44" s="15">
+        <v>40</v>
+      </c>
+      <c r="E44" s="15">
+        <v>0</v>
+      </c>
+      <c r="F44" s="15">
+        <v>0</v>
+      </c>
+      <c r="G44" s="15">
+        <v>0</v>
+      </c>
+      <c r="H44" s="15">
+        <v>20</v>
+      </c>
+      <c r="I44" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="14" t="str">
+        <v>640</v>
+      </c>
+      <c r="J44" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="45" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E25DDF4-1FA9-4621-831F-814DF4C24081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FE762F-7B71-49F0-ABE6-078934C50EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>NO PROGRESS</t>
+  </si>
+  <si>
+    <t>STARTED AGAIN</t>
   </si>
 </sst>
 </file>
@@ -2918,26 +2921,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="14" t="str">
+      <c r="A45" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B45" s="15">
+        <v>420</v>
+      </c>
+      <c r="C45" s="15">
+        <v>0</v>
+      </c>
+      <c r="D45" s="15">
+        <v>240</v>
+      </c>
+      <c r="E45" s="15">
+        <v>0</v>
+      </c>
+      <c r="F45" s="15">
+        <v>0</v>
+      </c>
+      <c r="G45" s="15">
+        <v>0</v>
+      </c>
+      <c r="H45" s="15">
+        <v>30</v>
+      </c>
+      <c r="I45" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="14" t="str">
+        <v>690</v>
+      </c>
+      <c r="J45" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>750</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="46" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FE762F-7B71-49F0-ABE6-078934C50EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95784686-CAFE-401B-AA74-3BB4898DA5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>STARTED AGAIN</t>
+  </si>
+  <si>
+    <t>HAPPY FAMILY</t>
   </si>
 </sst>
 </file>
@@ -2967,26 +2970,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="14" t="str">
+      <c r="A46" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B46" s="15">
+        <v>480</v>
+      </c>
+      <c r="C46" s="15">
+        <v>0</v>
+      </c>
+      <c r="D46" s="15">
+        <v>180</v>
+      </c>
+      <c r="E46" s="15">
+        <v>0</v>
+      </c>
+      <c r="F46" s="15">
+        <v>0</v>
+      </c>
+      <c r="G46" s="15">
+        <v>0</v>
+      </c>
+      <c r="H46" s="15">
+        <v>40</v>
+      </c>
+      <c r="I46" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="14" t="str">
+        <v>700</v>
+      </c>
+      <c r="J46" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="47" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95784686-CAFE-401B-AA74-3BB4898DA5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DC0764-EB21-4637-8C0D-825AC64443BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>HAPPY FAMILY</t>
+  </si>
+  <si>
+    <t>NOT CONSISTENT</t>
   </si>
 </sst>
 </file>
@@ -3016,26 +3019,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="14" t="str">
+      <c r="A47" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B47" s="15">
+        <v>420</v>
+      </c>
+      <c r="C47" s="15">
+        <v>0</v>
+      </c>
+      <c r="D47" s="15">
+        <v>240</v>
+      </c>
+      <c r="E47" s="15">
+        <v>0</v>
+      </c>
+      <c r="F47" s="15">
+        <v>0</v>
+      </c>
+      <c r="G47" s="15">
+        <v>0</v>
+      </c>
+      <c r="H47" s="15">
+        <v>50</v>
+      </c>
+      <c r="I47" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="14" t="str">
+        <v>710</v>
+      </c>
+      <c r="J47" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>730</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="48" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DC0764-EB21-4637-8C0D-825AC64443BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD7C30A-3F46-411A-9890-66D035D763E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>NOT CONSISTENT</t>
+  </si>
+  <si>
+    <t>BIKE SELFSERVICE</t>
   </si>
 </sst>
 </file>
@@ -3065,26 +3068,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="14" t="str">
+      <c r="A48" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B48" s="15">
+        <v>480</v>
+      </c>
+      <c r="C48" s="15">
+        <v>0</v>
+      </c>
+      <c r="D48" s="15">
+        <v>250</v>
+      </c>
+      <c r="E48" s="15">
+        <v>30</v>
+      </c>
+      <c r="F48" s="15">
+        <v>250</v>
+      </c>
+      <c r="G48" s="15">
+        <v>5</v>
+      </c>
+      <c r="H48" s="15">
+        <v>120</v>
+      </c>
+      <c r="I48" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="14" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J48" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="49" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD7C30A-3F46-411A-9890-66D035D763E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDFDFE5-4FEC-44C4-AB46-96243F962E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>BIKE SELFSERVICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MUNDANE</t>
   </si>
 </sst>
 </file>
@@ -3114,26 +3117,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="14" t="str">
+      <c r="A49" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B49" s="15">
+        <v>420</v>
+      </c>
+      <c r="C49" s="15">
+        <v>0</v>
+      </c>
+      <c r="D49" s="15">
+        <v>240</v>
+      </c>
+      <c r="E49" s="15">
+        <v>0</v>
+      </c>
+      <c r="F49" s="15">
+        <v>300</v>
+      </c>
+      <c r="G49" s="15">
+        <v>0</v>
+      </c>
+      <c r="H49" s="15">
+        <v>0</v>
+      </c>
+      <c r="I49" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J49" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="50" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDFDFE5-4FEC-44C4-AB46-96243F962E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DFDE33-BE66-4407-8422-A896A5D2A3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t xml:space="preserve"> MUNDANE</t>
+  </si>
+  <si>
+    <t>SIBLING TIME</t>
   </si>
 </sst>
 </file>
@@ -3163,26 +3166,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="14" t="str">
+      <c r="A50" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B50" s="15">
+        <v>440</v>
+      </c>
+      <c r="C50" s="15">
+        <v>0</v>
+      </c>
+      <c r="D50" s="15">
+        <v>0</v>
+      </c>
+      <c r="E50" s="15">
+        <v>0</v>
+      </c>
+      <c r="F50" s="15">
+        <v>0</v>
+      </c>
+      <c r="G50" s="15">
+        <v>0</v>
+      </c>
+      <c r="H50" s="15">
+        <v>100</v>
+      </c>
+      <c r="I50" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="14" t="str">
+        <v>540</v>
+      </c>
+      <c r="J50" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>900</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="51" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DFDE33-BE66-4407-8422-A896A5D2A3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51E1707-443C-44A9-8937-B7EC8823F83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3212,26 +3212,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="14" t="str">
+      <c r="A51" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B51" s="15">
+        <v>360</v>
+      </c>
+      <c r="C51" s="15">
+        <v>50</v>
+      </c>
+      <c r="D51" s="15">
+        <v>50</v>
+      </c>
+      <c r="E51" s="15">
+        <v>0</v>
+      </c>
+      <c r="F51" s="15">
+        <v>0</v>
+      </c>
+      <c r="G51" s="15">
+        <v>0</v>
+      </c>
+      <c r="H51" s="15">
+        <v>0</v>
+      </c>
+      <c r="I51" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="14" t="str">
+        <v>460</v>
+      </c>
+      <c r="J51" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>980</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="52" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51E1707-443C-44A9-8937-B7EC8823F83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFAAF8B-9B81-436C-B15C-933E09DD3319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>SIBLING TIME</t>
+  </si>
+  <si>
+    <t>DOING WELL</t>
   </si>
 </sst>
 </file>
@@ -3258,26 +3261,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="14" t="str">
+      <c r="A52" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B52" s="15">
+        <v>420</v>
+      </c>
+      <c r="C52" s="15">
+        <v>30</v>
+      </c>
+      <c r="D52" s="15">
+        <v>310</v>
+      </c>
+      <c r="E52" s="15">
+        <v>0</v>
+      </c>
+      <c r="F52" s="15">
+        <v>0</v>
+      </c>
+      <c r="G52" s="15">
+        <v>0</v>
+      </c>
+      <c r="H52" s="15">
+        <v>20</v>
+      </c>
+      <c r="I52" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="14" t="str">
+        <v>780</v>
+      </c>
+      <c r="J52" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="53" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFAAF8B-9B81-436C-B15C-933E09DD3319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBA511B-2714-4794-9E68-5337123A6F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>DOING WELL</t>
+  </si>
+  <si>
+    <t>BEING AT PEACE</t>
   </si>
 </sst>
 </file>
@@ -3307,26 +3310,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="14" t="str">
+      <c r="A53" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B53" s="15">
+        <v>360</v>
+      </c>
+      <c r="C53" s="15">
+        <v>0</v>
+      </c>
+      <c r="D53" s="15">
+        <v>240</v>
+      </c>
+      <c r="E53" s="15">
+        <v>0</v>
+      </c>
+      <c r="F53" s="15">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15">
+        <v>0</v>
+      </c>
+      <c r="H53" s="15">
+        <v>10</v>
+      </c>
+      <c r="I53" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="14" t="str">
+        <v>610</v>
+      </c>
+      <c r="J53" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>830</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="54" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBA511B-2714-4794-9E68-5337123A6F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDD835E-C814-4036-85B8-4A1AEEB020B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>BEING AT PEACE</t>
+  </si>
+  <si>
+    <t>LEARNING TO BELIEVE</t>
   </si>
 </sst>
 </file>
@@ -3356,26 +3359,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
-      <c r="I54" s="14" t="str">
+      <c r="A54" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B54" s="15">
+        <v>420</v>
+      </c>
+      <c r="C54" s="15">
+        <v>0</v>
+      </c>
+      <c r="D54" s="15">
+        <v>180</v>
+      </c>
+      <c r="E54" s="15">
+        <v>0</v>
+      </c>
+      <c r="F54" s="15">
+        <v>0</v>
+      </c>
+      <c r="G54" s="15">
+        <v>0</v>
+      </c>
+      <c r="H54" s="15">
+        <v>20</v>
+      </c>
+      <c r="I54" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="14" t="str">
+        <v>620</v>
+      </c>
+      <c r="J54" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="55" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDD835E-C814-4036-85B8-4A1AEEB020B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E866D28C-4B5A-4114-9A6F-1BE6C2BB8A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3405,26 +3405,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="14" t="str">
+      <c r="A55" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B55" s="15">
+        <v>360</v>
+      </c>
+      <c r="C55" s="15">
+        <v>0</v>
+      </c>
+      <c r="D55" s="15">
+        <v>120</v>
+      </c>
+      <c r="E55" s="15">
+        <v>0</v>
+      </c>
+      <c r="F55" s="15">
+        <v>0</v>
+      </c>
+      <c r="G55" s="15">
+        <v>0</v>
+      </c>
+      <c r="H55" s="15">
+        <v>10</v>
+      </c>
+      <c r="I55" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="14" t="str">
+        <v>490</v>
+      </c>
+      <c r="J55" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>950</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E866D28C-4B5A-4114-9A6F-1BE6C2BB8A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB1D61-092D-4D59-BC36-B516E3375EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>LEARNING TO BELIEVE</t>
+  </si>
+  <si>
+    <t>LAGING BEHIND</t>
   </si>
 </sst>
 </file>
@@ -3451,26 +3454,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
-      <c r="H56" s="15"/>
-      <c r="I56" s="14" t="str">
+      <c r="A56" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B56" s="15">
+        <v>480</v>
+      </c>
+      <c r="C56" s="15">
+        <v>0</v>
+      </c>
+      <c r="D56" s="15">
+        <v>180</v>
+      </c>
+      <c r="E56" s="15">
+        <v>0</v>
+      </c>
+      <c r="F56" s="15">
+        <v>0</v>
+      </c>
+      <c r="G56" s="15">
+        <v>0</v>
+      </c>
+      <c r="H56" s="15">
+        <v>20</v>
+      </c>
+      <c r="I56" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="14" t="str">
+        <v>680</v>
+      </c>
+      <c r="J56" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="57" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AB1D61-092D-4D59-BC36-B516E3375EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B24E99-A2ED-4567-9E54-16EB9803B85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>LAGING BEHIND</t>
+  </si>
+  <si>
+    <t>TRAVEL TIME</t>
   </si>
 </sst>
 </file>
@@ -3500,26 +3503,50 @@
       </c>
     </row>
     <row r="57" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
-      <c r="I57" s="14" t="str">
+      <c r="A57" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B57" s="15">
+        <v>430</v>
+      </c>
+      <c r="C57" s="15">
+        <v>10</v>
+      </c>
+      <c r="D57" s="15">
+        <v>180</v>
+      </c>
+      <c r="E57" s="15">
+        <v>10</v>
+      </c>
+      <c r="F57" s="15">
+        <v>0</v>
+      </c>
+      <c r="G57" s="15">
+        <v>0</v>
+      </c>
+      <c r="H57" s="15">
+        <v>10</v>
+      </c>
+      <c r="I57" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="14" t="str">
+        <v>640</v>
+      </c>
+      <c r="J57" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>800</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="58" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B24E99-A2ED-4567-9E54-16EB9803B85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABE3C5F-F9C2-4763-BAC1-2D7272BB30D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>TRAVEL TIME</t>
+  </si>
+  <si>
+    <t>READY FOR INTERVIEW</t>
   </si>
 </sst>
 </file>
@@ -3549,26 +3552,50 @@
       </c>
     </row>
     <row r="58" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
-      <c r="H58" s="15"/>
-      <c r="I58" s="14" t="str">
+      <c r="A58" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B58" s="15">
+        <v>360</v>
+      </c>
+      <c r="C58" s="15">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15">
+        <v>100</v>
+      </c>
+      <c r="E58" s="15">
+        <v>5</v>
+      </c>
+      <c r="F58" s="15">
+        <v>0</v>
+      </c>
+      <c r="G58" s="15">
+        <v>0</v>
+      </c>
+      <c r="H58" s="15">
+        <v>30</v>
+      </c>
+      <c r="I58" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="14" t="str">
+        <v>495</v>
+      </c>
+      <c r="J58" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>945</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="59" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABE3C5F-F9C2-4763-BAC1-2D7272BB30D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EED0EE-2673-45A7-A942-6CC6686DBEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>READY FOR INTERVIEW</t>
+  </si>
+  <si>
+    <t>DAY WENT WELL</t>
   </si>
 </sst>
 </file>
@@ -3598,26 +3601,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="13"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
-      <c r="I59" s="14" t="str">
+      <c r="A59" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B59" s="15">
+        <v>420</v>
+      </c>
+      <c r="C59" s="15">
+        <v>20</v>
+      </c>
+      <c r="D59" s="15">
+        <v>120</v>
+      </c>
+      <c r="E59" s="15">
+        <v>0</v>
+      </c>
+      <c r="F59" s="15">
+        <v>0</v>
+      </c>
+      <c r="G59" s="15">
+        <v>0</v>
+      </c>
+      <c r="H59" s="15">
+        <v>20</v>
+      </c>
+      <c r="I59" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="14" t="str">
+        <v>580</v>
+      </c>
+      <c r="J59" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>860</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="60" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>

--- a/12604000.xlsx
+++ b/12604000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khush\Desktop\PYTHON\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3EED0EE-2673-45A7-A942-6CC6686DBEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D41DD1-5F6E-4133-ACC9-1C17540DDD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>DAY WENT WELL</t>
+  </si>
+  <si>
+    <t>TRAVELING</t>
   </si>
 </sst>
 </file>
@@ -3647,26 +3650,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="13"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="15"/>
-      <c r="I60" s="14" t="str">
+      <c r="A60" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B60" s="15">
+        <v>380</v>
+      </c>
+      <c r="C60" s="15">
+        <v>0</v>
+      </c>
+      <c r="D60" s="15">
+        <v>140</v>
+      </c>
+      <c r="E60" s="15">
+        <v>0</v>
+      </c>
+      <c r="F60" s="15">
+        <v>0</v>
+      </c>
+      <c r="G60" s="15">
+        <v>0</v>
+      </c>
+      <c r="H60" s="15">
+        <v>50</v>
+      </c>
+      <c r="I60" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="14" t="str">
+        <v>570</v>
+      </c>
+      <c r="J60" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>870</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="61" spans="1:14" s="18" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="13"/>
